--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_024.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E52169FC-FBD8-47BA-94E2-4C347836786B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F8C5009-822A-49F3-BB3B-887461076306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -606,13 +606,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH03,S04aH03,S01aH03,S02aH03</t>
+    <t>S04aH03,S03aH03,S01aH03,S02aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH02,S04aH02,S04aH05,S02aH01,S01aH05,S03aH04,S01aH01,S04aH01,S03aH02,S01aH02,S04aH04,S03aH01,S03aH05,S02aH04,S02aH05,S01aH04</t>
+    <t>S02aH04,S02aH05,S02aH01,S03aH02,S01aH02,S04aH04,S01aH04,S02aH02,S04aH02,S04aH05,S03aH01,S01aH01,S04aH01,S01aH05,S03aH05,S03aH04</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH02,S04aH02,S04aH05,S02aH01,S01aH05,S03aH04,S01aH01,S04aH01,S03aH02,S01aH02,S04aH04,S03aH01,S03aH05,S02aH04,S02aH05,S01aH04</v>
+        <v>S02aH04,S02aH05,S02aH01,S03aH02,S01aH02,S04aH04,S01aH04,S02aH02,S04aH02,S04aH05,S03aH01,S01aH01,S04aH01,S01aH05,S03aH05,S03aH04</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH03,S04aH03,S01aH03,S02aH03</v>
+        <v>S04aH03,S03aH03,S01aH03,S02aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1335,7 +1335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B60E3734-AB91-4711-BE2A-98DD959A2473}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F037BD43-7E01-4311-A242-830E2594B8D1}">
   <dimension ref="A9:G15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1433,7 +1433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E109621D-F2FC-40B4-AD1B-55A567F73386}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C83371D-8FE1-40A3-9418-6E4FA69DB3A4}">
   <dimension ref="B9:O410"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14295,7 +14295,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD7128A-DE60-4CF8-B516-716DFD43B307}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98FA678E-2419-4159-BFB9-61B6D230277A}">
   <dimension ref="B9:CR60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22148,7 +22148,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05110439-F1FD-4D9E-9C75-88E02333EB59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C93E5A0-BC0F-4BD5-B11D-3001E6DE9D54}">
   <dimension ref="B9:E30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22458,7 +22458,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{741E48FF-688A-44DB-8FD9-8721FCB1808A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BDD8B12-F8CD-4678-94EB-71BC04F78E25}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22925,7 +22925,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3964388D-66C7-4A90-BAFD-BBE744073C44}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46E606F8-9E70-4AFD-AE0F-0B89652133C9}">
   <dimension ref="B9:D30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23172,7 +23172,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE9C436-88B4-40EB-9BEA-0B13B31AD963}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E744A160-0AD4-41B6-BF06-458E25D55F76}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23512,7 +23512,7 @@
         <v>43</v>
       </c>
       <c r="D33">
-        <v>0.2365142857142857</v>
+        <v>0.23651428571428568</v>
       </c>
       <c r="E33" t="s">
         <v>196</v>
@@ -23582,7 +23582,7 @@
         <v>45</v>
       </c>
       <c r="D38">
-        <v>0.22297500000000001</v>
+        <v>0.22297499999999998</v>
       </c>
       <c r="E38" t="s">
         <v>196</v>
@@ -23638,7 +23638,7 @@
         <v>45</v>
       </c>
       <c r="D42">
-        <v>0.29354999999999998</v>
+        <v>0.29355000000000003</v>
       </c>
       <c r="E42" t="s">
         <v>196</v>
@@ -23848,7 +23848,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.24679999999999996</v>
+        <v>0.24680000000000005</v>
       </c>
       <c r="E57" t="s">
         <v>196</v>
@@ -24072,7 +24072,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.25780000000000003</v>
+        <v>0.25779999999999997</v>
       </c>
       <c r="E73" t="s">
         <v>196</v>
@@ -24198,7 +24198,7 @@
         <v>45</v>
       </c>
       <c r="D82">
-        <v>0.21397499999999997</v>
+        <v>0.213975</v>
       </c>
       <c r="E82" t="s">
         <v>196</v>
@@ -24352,7 +24352,7 @@
         <v>43</v>
       </c>
       <c r="D93">
-        <v>0.25259999999999999</v>
+        <v>0.25260000000000005</v>
       </c>
       <c r="E93" t="s">
         <v>196</v>
@@ -24366,7 +24366,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.23267499999999997</v>
+        <v>0.23267500000000002</v>
       </c>
       <c r="E94" t="s">
         <v>196</v>
@@ -24520,7 +24520,7 @@
         <v>43</v>
       </c>
       <c r="D105">
-        <v>0.24881428571428571</v>
+        <v>0.24881428571428568</v>
       </c>
       <c r="E105" t="s">
         <v>196</v>
@@ -24758,7 +24758,7 @@
         <v>45</v>
       </c>
       <c r="D122">
-        <v>0.24012499999999998</v>
+        <v>0.24012500000000001</v>
       </c>
       <c r="E122" t="s">
         <v>196</v>
@@ -24814,7 +24814,7 @@
         <v>45</v>
       </c>
       <c r="D126">
-        <v>0.22469999999999998</v>
+        <v>0.22470000000000001</v>
       </c>
       <c r="E126" t="s">
         <v>196</v>
